--- a/output/roomself_excel/7620.xlsx
+++ b/output/roomself_excel/7620.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>148920</v>
+        <v>189618</v>
       </c>
       <c r="D2" t="n">
-        <v>3112</v>
+        <v>3544</v>
       </c>
       <c r="E2" t="n">
-        <v>806</v>
+        <v>451</v>
       </c>
       <c r="F2" t="n">
-        <v>392</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>116063</v>
+        <v>261277</v>
       </c>
       <c r="D3" t="n">
-        <v>2784</v>
+        <v>4155</v>
       </c>
       <c r="E3" t="n">
-        <v>444</v>
+        <v>607</v>
       </c>
       <c r="F3" t="n">
-        <v>305</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>514055</v>
+        <v>116063</v>
       </c>
       <c r="D4" t="n">
-        <v>8063</v>
+        <v>2784</v>
       </c>
       <c r="E4" t="n">
-        <v>932</v>
+        <v>444</v>
       </c>
       <c r="F4" t="n">
-        <v>674</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>74304</v>
+        <v>133056</v>
       </c>
       <c r="D5" t="n">
-        <v>2416</v>
+        <v>2960</v>
       </c>
       <c r="E5" t="n">
-        <v>459</v>
+        <v>294</v>
       </c>
       <c r="F5" t="n">
-        <v>200</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>133056</v>
+        <v>112347</v>
       </c>
       <c r="D6" t="n">
-        <v>2960</v>
+        <v>2864</v>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>381</v>
       </c>
       <c r="F6" t="n">
-        <v>297</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16402</v>
+        <v>23074</v>
       </c>
       <c r="D7" t="n">
-        <v>1028</v>
+        <v>1220</v>
       </c>
       <c r="E7" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15429</v>
+        <v>17880</v>
       </c>
       <c r="D8" t="n">
-        <v>1000</v>
+        <v>1076</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23074</v>
+        <v>40043</v>
       </c>
       <c r="D9" t="n">
-        <v>1220</v>
+        <v>1644</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>112347</v>
+        <v>16402</v>
       </c>
       <c r="D10" t="n">
-        <v>2864</v>
+        <v>1028</v>
       </c>
       <c r="E10" t="n">
-        <v>394</v>
+        <v>139</v>
       </c>
       <c r="F10" t="n">
-        <v>322</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>98988</v>
+        <v>15429</v>
       </c>
       <c r="D11" t="n">
-        <v>2524</v>
+        <v>1000</v>
       </c>
       <c r="E11" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>155728</v>
+        <v>148920</v>
       </c>
       <c r="D12" t="n">
-        <v>3780</v>
+        <v>3112</v>
       </c>
       <c r="E12" t="n">
-        <v>729</v>
+        <v>464</v>
       </c>
       <c r="F12" t="n">
-        <v>425</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17880</v>
+        <v>74304</v>
       </c>
       <c r="D13" t="n">
-        <v>1076</v>
+        <v>2416</v>
       </c>
       <c r="E13" t="n">
-        <v>176</v>
+        <v>459</v>
       </c>
       <c r="F13" t="n">
-        <v>145</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14">
@@ -730,17 +730,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>40043</v>
+        <v>63160</v>
       </c>
       <c r="D14" t="n">
-        <v>1644</v>
+        <v>2156</v>
       </c>
       <c r="E14" t="n">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="F14" t="n">
         <v>25</v>
@@ -756,15 +756,59 @@
         </is>
       </c>
       <c r="C15" t="n">
+        <v>98988</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2524</v>
+      </c>
+      <c r="E15" t="n">
+        <v>392</v>
+      </c>
+      <c r="F15" t="n">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>155728</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3780</v>
+      </c>
+      <c r="E16" t="n">
+        <v>572</v>
+      </c>
+      <c r="F16" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>37736</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D17" t="n">
         <v>1560</v>
       </c>
-      <c r="E15" t="n">
-        <v>425</v>
-      </c>
-      <c r="F15" t="n">
+      <c r="E17" t="n">
+        <v>237</v>
+      </c>
+      <c r="F17" t="n">
         <v>203</v>
       </c>
     </row>

--- a/output/roomself_excel/7620.xlsx
+++ b/output/roomself_excel/7620.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>3544</v>
       </c>
-      <c r="E2" t="n">
-        <v>451</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>141</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>426</v>
+      </c>
+      <c r="J2" t="n">
+        <v>25</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +551,23 @@
       <c r="D3" t="n">
         <v>4155</v>
       </c>
-      <c r="E3" t="n">
-        <v>607</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
+        <v>598</v>
+      </c>
+      <c r="G3" t="n">
         <v>28</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +584,31 @@
       <c r="D4" t="n">
         <v>2784</v>
       </c>
-      <c r="E4" t="n">
-        <v>444</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>305</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="G4" t="n">
+        <v>28</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>277</v>
+      </c>
+      <c r="J4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +625,23 @@
       <c r="D5" t="n">
         <v>2960</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>294</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>27</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +658,31 @@
       <c r="D6" t="n">
         <v>2864</v>
       </c>
-      <c r="E6" t="n">
-        <v>381</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>322</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="G6" t="n">
+        <v>25</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>355</v>
+      </c>
+      <c r="J6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +699,15 @@
       <c r="D7" t="n">
         <v>1220</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +724,31 @@
       <c r="D8" t="n">
         <v>1076</v>
       </c>
-      <c r="E8" t="n">
-        <v>176</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>145</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G8" t="n">
+        <v>27</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>149</v>
+      </c>
+      <c r="J8" t="n">
+        <v>25</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +765,23 @@
       <c r="D9" t="n">
         <v>1644</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>199</v>
       </c>
-      <c r="F9" t="n">
-        <v>25</v>
-      </c>
+      <c r="G9" t="n">
+        <v>25</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +798,23 @@
       <c r="D10" t="n">
         <v>1028</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>139</v>
       </c>
-      <c r="F10" t="n">
-        <v>25</v>
-      </c>
+      <c r="G10" t="n">
+        <v>25</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +831,15 @@
       <c r="D11" t="n">
         <v>1000</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +856,31 @@
       <c r="D12" t="n">
         <v>3112</v>
       </c>
-      <c r="E12" t="n">
-        <v>464</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>392</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="G12" t="n">
+        <v>26</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>876</v>
+      </c>
+      <c r="J12" t="n">
+        <v>26</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +897,31 @@
       <c r="D13" t="n">
         <v>2416</v>
       </c>
-      <c r="E13" t="n">
-        <v>459</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>200</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="G13" t="n">
+        <v>28</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>163</v>
+      </c>
+      <c r="J13" t="n">
+        <v>27</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +938,23 @@
       <c r="D14" t="n">
         <v>2156</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>219</v>
       </c>
-      <c r="F14" t="n">
-        <v>25</v>
-      </c>
+      <c r="G14" t="n">
+        <v>25</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,11 +971,38 @@
       <c r="D15" t="n">
         <v>2524</v>
       </c>
-      <c r="E15" t="n">
-        <v>392</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>317</v>
+        <v>292</v>
+      </c>
+      <c r="G15" t="n">
+        <v>28</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>292</v>
+      </c>
+      <c r="J15" t="n">
+        <v>25</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>339</v>
+      </c>
+      <c r="M15" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="16">
@@ -783,12 +1020,31 @@
       <c r="D16" t="n">
         <v>3780</v>
       </c>
-      <c r="E16" t="n">
-        <v>572</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>425</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="G16" t="n">
+        <v>27</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>303</v>
+      </c>
+      <c r="J16" t="n">
+        <v>25</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1061,31 @@
       <c r="D17" t="n">
         <v>1560</v>
       </c>
-      <c r="E17" t="n">
-        <v>237</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>203</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="G17" t="n">
+        <v>25</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>178</v>
+      </c>
+      <c r="J17" t="n">
+        <v>25</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
